--- a/proveedores.xlsx
+++ b/proveedores.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4998"/>
+  <dimension ref="A1:H5005"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="13.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11966,7 +11966,6 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" t="inlineStr"/>
       <c r="B798" t="n">
         <v>22</v>
       </c>
@@ -11975,7 +11974,6 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" t="inlineStr"/>
       <c r="B799" t="n">
         <v>22</v>
       </c>
@@ -11984,7 +11982,6 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" t="inlineStr"/>
       <c r="B800" t="n">
         <v>22</v>
       </c>
@@ -11993,7 +11990,6 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" t="inlineStr"/>
       <c r="B801" t="n">
         <v>22</v>
       </c>
@@ -12015,7 +12011,6 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" t="inlineStr"/>
       <c r="B803" t="n">
         <v>0</v>
       </c>
@@ -12037,7 +12032,6 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" t="inlineStr"/>
       <c r="B805" t="n">
         <v>0</v>
       </c>
@@ -12046,7 +12040,6 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" t="inlineStr"/>
       <c r="B806" t="n">
         <v>0</v>
       </c>
@@ -12757,7 +12750,6 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" t="inlineStr"/>
       <c r="B861" t="n">
         <v>22</v>
       </c>
@@ -12766,7 +12758,6 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" t="inlineStr"/>
       <c r="B862" t="n">
         <v>0</v>
       </c>
@@ -19288,7 +19279,6 @@
       </c>
     </row>
     <row r="1364">
-      <c r="A1364" t="inlineStr"/>
       <c r="B1364" t="n">
         <v>0</v>
       </c>
@@ -33103,7 +33093,6 @@
       </c>
     </row>
     <row r="2427">
-      <c r="A2427" t="inlineStr"/>
       <c r="B2427" t="n">
         <v>0</v>
       </c>
@@ -35855,7 +35844,6 @@
       </c>
     </row>
     <row r="2639">
-      <c r="A2639" t="inlineStr"/>
       <c r="B2639" t="n">
         <v>0</v>
       </c>
@@ -36423,7 +36411,6 @@
       </c>
     </row>
     <row r="2683">
-      <c r="A2683" t="inlineStr"/>
       <c r="B2683" t="n">
         <v>0</v>
       </c>
@@ -37771,7 +37758,6 @@
       </c>
     </row>
     <row r="2787">
-      <c r="A2787" t="inlineStr"/>
       <c r="B2787" t="n">
         <v>0</v>
       </c>
@@ -38079,7 +38065,6 @@
       </c>
     </row>
     <row r="2811">
-      <c r="A2811" t="inlineStr"/>
       <c r="B2811" t="n">
         <v>0</v>
       </c>
@@ -47136,7 +47121,6 @@
       </c>
     </row>
     <row r="3508">
-      <c r="A3508" t="inlineStr"/>
       <c r="B3508" t="n">
         <v>0</v>
       </c>
@@ -51415,10 +51399,10 @@
         </is>
       </c>
       <c r="B3837" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3837" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3838">
@@ -54711,7 +54695,6 @@
       </c>
     </row>
     <row r="4091">
-      <c r="A4091" t="inlineStr"/>
       <c r="B4091" t="n">
         <v>0</v>
       </c>
@@ -57853,7 +57836,6 @@
       </c>
     </row>
     <row r="4333">
-      <c r="A4333" t="inlineStr"/>
       <c r="B4333" t="n">
         <v>0</v>
       </c>
@@ -58044,7 +58026,6 @@
       </c>
     </row>
     <row r="4348">
-      <c r="A4348" t="inlineStr"/>
       <c r="B4348" t="n">
         <v>0</v>
       </c>
@@ -58092,7 +58073,6 @@
       </c>
     </row>
     <row r="4352">
-      <c r="A4352" t="inlineStr"/>
       <c r="B4352" t="n">
         <v>0</v>
       </c>
@@ -58374,7 +58354,6 @@
       </c>
     </row>
     <row r="4374">
-      <c r="A4374" t="inlineStr"/>
       <c r="B4374" t="n">
         <v>0</v>
       </c>
@@ -58500,7 +58479,6 @@
       </c>
     </row>
     <row r="4384">
-      <c r="A4384" t="inlineStr"/>
       <c r="B4384" t="n">
         <v>0</v>
       </c>
@@ -59562,7 +59540,6 @@
       </c>
     </row>
     <row r="4466">
-      <c r="A4466" t="inlineStr"/>
       <c r="B4466" t="n">
         <v>0</v>
       </c>
@@ -62093,7 +62070,6 @@
       </c>
     </row>
     <row r="4661">
-      <c r="A4661" t="inlineStr"/>
       <c r="B4661" t="n">
         <v>0</v>
       </c>
@@ -65014,7 +64990,6 @@
       </c>
     </row>
     <row r="4886">
-      <c r="A4886" t="inlineStr"/>
       <c r="B4886" t="n">
         <v>0</v>
       </c>
@@ -65179,7 +65154,6 @@
       </c>
     </row>
     <row r="4899">
-      <c r="A4899" t="inlineStr"/>
       <c r="B4899" t="n">
         <v>0</v>
       </c>
@@ -66472,6 +66446,97 @@
       </c>
       <c r="D4998" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="4999">
+      <c r="A4999" t="inlineStr">
+        <is>
+          <t>20206736276</t>
+        </is>
+      </c>
+      <c r="B4999" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4999" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5000">
+      <c r="A5000" t="inlineStr">
+        <is>
+          <t>20285632448</t>
+        </is>
+      </c>
+      <c r="B5000" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5000" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5001">
+      <c r="A5001" t="inlineStr">
+        <is>
+          <t>20131149248</t>
+        </is>
+      </c>
+      <c r="B5001" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5001" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5002">
+      <c r="A5002" t="inlineStr">
+        <is>
+          <t>20164301797</t>
+        </is>
+      </c>
+      <c r="B5002" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5002" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5003">
+      <c r="A5003" t="inlineStr">
+        <is>
+          <t>23167820719</t>
+        </is>
+      </c>
+      <c r="B5003" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5003" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5004">
+      <c r="A5004" t="inlineStr">
+        <is>
+          <t>20104183671</t>
+        </is>
+      </c>
+      <c r="B5004" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5004" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5005">
+      <c r="A5005" t="inlineStr">
+        <is>
+          <t>24284239918</t>
+        </is>
+      </c>
+      <c r="B5005" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5005" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/proveedores.xlsx
+++ b/proveedores.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5005"/>
+  <dimension ref="A1:H5015"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="13.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -39561,10 +39561,10 @@
         </is>
       </c>
       <c r="B2926" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2926" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2927">
@@ -50957,10 +50957,10 @@
         </is>
       </c>
       <c r="B3803" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3803" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3804">
@@ -66537,6 +66537,136 @@
       </c>
       <c r="D5005" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5006">
+      <c r="A5006" t="inlineStr">
+        <is>
+          <t>30714439304</t>
+        </is>
+      </c>
+      <c r="B5006" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5006" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5007">
+      <c r="A5007" t="inlineStr">
+        <is>
+          <t>20373443515</t>
+        </is>
+      </c>
+      <c r="B5007" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5007" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5008">
+      <c r="A5008" t="inlineStr">
+        <is>
+          <t>23389167649</t>
+        </is>
+      </c>
+      <c r="B5008" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5008" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5009">
+      <c r="A5009" t="inlineStr">
+        <is>
+          <t>20124747318</t>
+        </is>
+      </c>
+      <c r="B5009" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5009" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5010">
+      <c r="A5010" t="inlineStr">
+        <is>
+          <t>20332711432</t>
+        </is>
+      </c>
+      <c r="B5010" t="n">
+        <v>54</v>
+      </c>
+      <c r="D5010" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5011">
+      <c r="A5011" t="inlineStr">
+        <is>
+          <t>20267967254</t>
+        </is>
+      </c>
+      <c r="B5011" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5011" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5012">
+      <c r="A5012" t="inlineStr">
+        <is>
+          <t>20224756020</t>
+        </is>
+      </c>
+      <c r="B5012" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5012" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5013">
+      <c r="A5013" t="inlineStr">
+        <is>
+          <t>20217048541</t>
+        </is>
+      </c>
+      <c r="B5013" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5013" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5014">
+      <c r="A5014" t="inlineStr">
+        <is>
+          <t>20120633210</t>
+        </is>
+      </c>
+      <c r="B5014" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5014" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5015">
+      <c r="A5015" t="inlineStr">
+        <is>
+          <t>30586347760</t>
+        </is>
+      </c>
+      <c r="B5015" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5015" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/proveedores.xlsx
+++ b/proveedores.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5015"/>
+  <dimension ref="A1:H5025"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="13.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -66338,10 +66338,10 @@
         </is>
       </c>
       <c r="B4990" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4990" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4991">
@@ -66667,6 +66667,136 @@
       </c>
       <c r="D5015" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="5016">
+      <c r="A5016" t="inlineStr">
+        <is>
+          <t>30719266017</t>
+        </is>
+      </c>
+      <c r="B5016" t="n">
+        <v>54</v>
+      </c>
+      <c r="D5016" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5017">
+      <c r="A5017" t="inlineStr">
+        <is>
+          <t>20459484915</t>
+        </is>
+      </c>
+      <c r="B5017" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5017" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5018">
+      <c r="A5018" t="inlineStr">
+        <is>
+          <t>20180846825</t>
+        </is>
+      </c>
+      <c r="B5018" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5018" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5019">
+      <c r="A5019" t="inlineStr">
+        <is>
+          <t>20164000495</t>
+        </is>
+      </c>
+      <c r="B5019" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5019" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5020">
+      <c r="A5020" t="inlineStr">
+        <is>
+          <t>30657282207</t>
+        </is>
+      </c>
+      <c r="B5020" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5020" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5021">
+      <c r="A5021" t="inlineStr">
+        <is>
+          <t>30516150641</t>
+        </is>
+      </c>
+      <c r="B5021" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5021" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5022">
+      <c r="A5022" t="inlineStr">
+        <is>
+          <t>30711824975</t>
+        </is>
+      </c>
+      <c r="B5022" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5022" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5023">
+      <c r="A5023" t="inlineStr">
+        <is>
+          <t>20223875646</t>
+        </is>
+      </c>
+      <c r="B5023" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5023" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5024">
+      <c r="A5024" t="inlineStr">
+        <is>
+          <t>20395783832</t>
+        </is>
+      </c>
+      <c r="B5024" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5024" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5025">
+      <c r="A5025" t="inlineStr">
+        <is>
+          <t>27223189011</t>
+        </is>
+      </c>
+      <c r="B5025" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5025" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/proveedores.xlsx
+++ b/proveedores.xlsx
@@ -66338,10 +66338,10 @@
         </is>
       </c>
       <c r="B4990" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D4990" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4991">
